--- a/data/base_ferreira_chagas.xlsx
+++ b/data/base_ferreira_chagas.xlsx
@@ -1,15 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7143A5-C355-4472-89F3-E25AC16AF89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -88,8 +95,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,13 +159,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +211,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,6 +245,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -264,9 +280,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -439,11 +456,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,4 +534,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A4D8C6-13C7-48A1-9FAF-58361C484CCF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/base_ferreira_chagas.xlsx
+++ b/data/base_ferreira_chagas.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7143A5-C355-4472-89F3-E25AC16AF89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34298127-66CD-4B51-860A-DE1FFD511793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
+    <sheet name="Funil_3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
   <si>
     <t>Data</t>
   </si>
@@ -543,4 +544,85 @@
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4769C81-919C-4957-9620-AB5BFDE2BB8C}">
+  <dimension ref="A1:W1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>